--- a/artfynd/A 13059-2022 artfynd.xlsx
+++ b/artfynd/A 13059-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13059-2022 artfynd.xlsx
+++ b/artfynd/A 13059-2022 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>133848546</v>
       </c>
       <c r="B4" t="n">
-        <v>92352</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133848537</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>133848545</v>
       </c>
       <c r="B6" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>133848535</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>133848544</v>
       </c>
       <c r="B8" t="n">
-        <v>91971</v>
+        <v>91978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>133848536</v>
       </c>
       <c r="B9" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 13059-2022 artfynd.xlsx
+++ b/artfynd/A 13059-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104506408</v>
+        <v>133848545</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600695.7178153944</v>
+        <v>600445</v>
       </c>
       <c r="R2" t="n">
-        <v>7035967.703365394</v>
+        <v>7035834</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>105166426</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600551.987842466</v>
+        <v>600552</v>
       </c>
       <c r="R3" t="n">
-        <v>7035803.731945802</v>
+        <v>7035804</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +844,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133848546</v>
+        <v>133848537</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600477</v>
+        <v>600559</v>
       </c>
       <c r="R4" t="n">
-        <v>7035868</v>
+        <v>7035984</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -988,7 +956,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133848537</v>
+        <v>133848544</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600559</v>
+        <v>600471</v>
       </c>
       <c r="R5" t="n">
-        <v>7035984</v>
+        <v>7035838</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1112,48 +1079,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133848545</v>
+        <v>104505435</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backsjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600445</v>
+        <v>600696</v>
       </c>
       <c r="R6" t="n">
-        <v>7035834</v>
+        <v>7035968</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,12 +1145,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2022-11-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,48 +1170,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133848535</v>
+        <v>133848536</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600518</v>
+        <v>600658</v>
       </c>
       <c r="R7" t="n">
-        <v>7035948</v>
+        <v>7036070</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1314,32 +1283,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133848544</v>
+        <v>133848535</v>
       </c>
       <c r="B8" t="n">
-        <v>91978</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1318,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600471</v>
+        <v>600518</v>
       </c>
       <c r="R8" t="n">
-        <v>7035838</v>
+        <v>7035948</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1415,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133848536</v>
+        <v>133848546</v>
       </c>
       <c r="B9" t="n">
-        <v>80481</v>
+        <v>92366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1426,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6040186</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1450,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600658</v>
+        <v>600477</v>
       </c>
       <c r="R9" t="n">
-        <v>7036070</v>
+        <v>7035868</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1494,6 +1463,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13059-2022 artfynd.xlsx
+++ b/artfynd/A 13059-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133848545</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133848537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133848544</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505435</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133848536</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133848535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,8 +1523,23 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133848546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>